--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2">
         <v>852</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D3">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>852</v>
